--- a/tasks/cross_device/linux_smarthome_assets/linux_smarthome_670/source/linux_1/tmp/protection/plan-audit.xlsx
+++ b/tasks/cross_device/linux_smarthome_assets/linux_smarthome_670/source/linux_1/tmp/protection/plan-audit.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Cancel plans matched by a protected-time rule; keep plans outside those rules. Final Status records the resulting native plan status.</t>
+          <t>Cancel plans matched by a protected-time rule; keep plans outside those rules. Final Status records the resulting native plan status. Matched Rule must be one of: protected - no exception; allowed quiet exception; not protected.</t>
         </is>
       </c>
     </row>
